--- a/TouhouSurvival/Assets/StreamingAssets/AttributeTables/Abilities/Passives/Moscow/moscow_exp.xlsx
+++ b/TouhouSurvival/Assets/StreamingAssets/AttributeTables/Abilities/Passives/Moscow/moscow_exp.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\TouhouSurvival\TouhouSurvival\Assets\StreamingAssets\AttributeTables\Abilities\Passives\Moscow\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Github\TouhouSurvival\TouhouSurvival\Assets\StreamingAssets\AttributeTables\Abilities\Passives\Moscow\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1BE88FA-84A0-4A19-998E-2E1ECF30B029}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A28DA267-25C9-4762-94A4-1FC07174C09B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7545" yWindow="2115" windowWidth="19395" windowHeight="12360" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11085" yWindow="5355" windowWidth="28800" windowHeight="17145" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="modifiers" sheetId="2" r:id="rId1"/>
@@ -42,10 +42,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>ExpGainIncrease</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>PercentAdd</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -55,6 +51,10 @@
   </si>
   <si>
     <t>경험치 획득량 30%p 증가</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ExpGain</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -407,16 +407,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C2">
         <v>0.2</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -424,16 +424,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C3">
         <v>0.3</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
